--- a/output/pdf_financials_xlsx/TI.xlsx
+++ b/output/pdf_financials_xlsx/TI.xlsx
@@ -925,22 +925,22 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.06639399999999999</v>
+        <v>-0.06639399999999999</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>11.031</v>
+        <v>-11.031</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>15.857</v>
+        <v>-15.857</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>10.886</v>
+        <v>-10.886</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>1.274</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>24661.526</v>
+        <v>-24661.526</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>-11.47</v>
@@ -1097,22 +1097,22 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.06639399999999999</v>
+        <v>-0.06639399999999999</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>11.031</v>
+        <v>-11.031</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>15.857</v>
+        <v>-15.857</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>10.886</v>
+        <v>-10.886</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>1.274</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>24661.526</v>
+        <v>-24661.526</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>-11.47</v>
@@ -1199,22 +1199,22 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.06639399999999999</v>
+        <v>-0.06639399999999999</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>11.031</v>
+        <v>-11.031</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>15.857</v>
+        <v>-15.857</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>10.886</v>
+        <v>-10.886</v>
       </c>
       <c r="F23" s="3" t="n">
         <v>1.274</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>24661.526</v>
+        <v>-24661.526</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>-11.47</v>
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>68.94374999999999</v>
+        <v>-68.94374999999999</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>99.10625</v>
+        <v>-99.10625</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>108.86</v>
+        <v>-108.86</v>
       </c>
       <c r="F26" s="1" t="inlineStr">
         <is>
@@ -1353,22 +1353,22 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.06639399999999999</v>
+        <v>-0.06639399999999999</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>11.031</v>
+        <v>-11.031</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>15.857</v>
+        <v>-15.857</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>10.886</v>
+        <v>-10.886</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>1.274</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>24661.526</v>
+        <v>-24661.526</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>-11.47</v>
@@ -1421,22 +1421,22 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.06639399999999999</v>
+        <v>-0.06639399999999999</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>12.01</v>
+        <v>-10.052</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>15.857</v>
+        <v>-15.857</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>10.886</v>
+        <v>-10.886</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>1.274</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>24661.526</v>
+        <v>-24661.526</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>-11.47</v>
@@ -1478,7 +1478,7 @@
         <v>2.291614202971544</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>39737.55820885902</v>
+        <v>-39737.55820885902</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>-22.02127251084745</v>
@@ -1497,22 +1497,22 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>-0</v>
@@ -1554,7 +1554,7 @@
         <v>2.291614202971544</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>39737.55820885902</v>
+        <v>-39737.55820885902</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>-22.02127251084745</v>
@@ -3588,31 +3588,31 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>-0.07738200000000001</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.745</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>2.335</v>
       </c>
       <c r="E92" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>7.843</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>6.504</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>6.245</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>4.971</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>5.093</v>
       </c>
     </row>
     <row r="93">
@@ -3814,13 +3814,13 @@
         <v>1.274</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>24661.526</v>
+        <v>-24661.526</v>
       </c>
       <c r="H99" s="3" t="n">
         <v>-10.196</v>
       </c>
       <c r="I99" s="3" t="n">
-        <v>6.717</v>
+        <v>-6.717</v>
       </c>
       <c r="J99" s="3" t="n">
         <v>-0.164</v>
@@ -3953,10 +3953,10 @@
         <v>0</v>
       </c>
       <c r="H103" s="3" t="n">
-        <v>0</v>
+        <v>0.415</v>
       </c>
       <c r="I103" s="3" t="n">
-        <v>0</v>
+        <v>-0.78</v>
       </c>
       <c r="J103" s="3" t="n">
         <v>0</v>
@@ -4055,10 +4055,10 @@
         <v>-1.955</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>-1.855</v>
+        <v>-1.44</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>-2.043</v>
+        <v>-2.823</v>
       </c>
       <c r="J106" s="3" t="n">
         <v>0.243</v>
@@ -5370,7 +5370,11 @@
           <t>Prepaids and deposits 11</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>-</t>
@@ -6495,7 +6499,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>-</t>
@@ -6874,7 +6882,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>-</t>
@@ -10840,7 +10852,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E97" s="5" t="n">
         <v>-0.07738200000000001</v>
       </c>
@@ -13639,7 +13655,7 @@
         <v>-10.196</v>
       </c>
       <c r="L143" s="5" t="n">
-        <v>6.717</v>
+        <v>-6.717</v>
       </c>
       <c r="M143" t="inlineStr">
         <is>
@@ -14328,7 +14344,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr"/>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E155" t="inlineStr">
         <is>
           <t>-</t>
@@ -25089,10 +25109,10 @@
         </is>
       </c>
       <c r="J333" s="5" t="n">
-        <v>24661.526</v>
+        <v>-24661.526</v>
       </c>
       <c r="K333" s="5" t="n">
-        <v>114701.26</v>
+        <v>-114701.26</v>
       </c>
       <c r="L333" t="inlineStr">
         <is>
@@ -27006,10 +27026,10 @@
         </is>
       </c>
       <c r="G365" s="5" t="n">
-        <v>15.857</v>
+        <v>-15.857</v>
       </c>
       <c r="H365" s="5" t="n">
-        <v>10.886</v>
+        <v>-10.886</v>
       </c>
       <c r="I365" t="inlineStr">
         <is>
@@ -27121,13 +27141,13 @@
         </is>
       </c>
       <c r="F367" s="5" t="n">
-        <v>11.164</v>
+        <v>-11.164</v>
       </c>
       <c r="G367" s="5" t="n">
-        <v>16.052</v>
+        <v>-16.052</v>
       </c>
       <c r="H367" s="5" t="n">
-        <v>11.383</v>
+        <v>-11.383</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -27782,10 +27802,10 @@
         </is>
       </c>
       <c r="F378" s="5" t="n">
-        <v>11.031</v>
+        <v>-11.031</v>
       </c>
       <c r="G378" s="5" t="n">
-        <v>15.857</v>
+        <v>-15.857</v>
       </c>
       <c r="H378" t="inlineStr">
         <is>
@@ -28960,10 +28980,10 @@
         </is>
       </c>
       <c r="E397" s="5" t="n">
-        <v>0.06639399999999999</v>
+        <v>-0.06639399999999999</v>
       </c>
       <c r="F397" s="5" t="n">
-        <v>11.031348</v>
+        <v>-11.031348</v>
       </c>
       <c r="G397" t="inlineStr">
         <is>
@@ -29082,10 +29102,10 @@
         </is>
       </c>
       <c r="E399" s="5" t="n">
-        <v>0.143776</v>
+        <v>-0.143776</v>
       </c>
       <c r="F399" s="5" t="n">
-        <v>11.164506</v>
+        <v>-11.164506</v>
       </c>
       <c r="G399" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/TI.xlsx
+++ b/output/pdf_financials_xlsx/TI.xlsx
@@ -789,31 +789,31 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.003746</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.078</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.111</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.035</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-0.155</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-0.234</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.315</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.322</v>
       </c>
     </row>
     <row r="13">
@@ -1353,31 +1353,31 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.06639399999999999</v>
+        <v>-0.062648</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-11.031</v>
+        <v>-10.953</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-15.857</v>
+        <v>-15.746</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-10.886</v>
+        <v>-10.851</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>1.274</v>
+        <v>1.284</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-24661.526</v>
+        <v>-24661.371</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-11.47</v>
+        <v>-11.236</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>4.814</v>
+        <v>4.499</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.164</v>
+        <v>-0.486</v>
       </c>
     </row>
     <row r="28">
@@ -1421,31 +1421,31 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.06639399999999999</v>
+        <v>-0.062648</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-10.052</v>
+        <v>-9.974</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-15.857</v>
+        <v>-15.746</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-10.886</v>
+        <v>-10.851</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>1.274</v>
+        <v>1.284</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-24661.526</v>
+        <v>-24661.371</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-11.47</v>
+        <v>-11.236</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>4.814</v>
+        <v>4.499</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.164</v>
+        <v>-0.486</v>
       </c>
     </row>
     <row r="30">
@@ -1475,19 +1475,19 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>2.291614202971544</v>
+        <v>2.309601755585135</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-39737.55820885902</v>
+        <v>-39737.30845458501</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-22.02127251084745</v>
+        <v>-21.57201551280574</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>7.486664282048491</v>
+        <v>6.996780765462435</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-0.2209170752734522</v>
+        <v>-0.6546688937981572</v>
       </c>
     </row>
     <row r="31">
@@ -21988,7 +21988,11 @@
           <t>General and administration expenses 8a</t>
         </is>
       </c>
-      <c r="D281" t="inlineStr"/>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E281" t="inlineStr">
         <is>
           <t>-</t>
@@ -22348,7 +22352,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
@@ -23831,7 +23835,11 @@
           <t>General and administration expenses 7a</t>
         </is>
       </c>
-      <c r="D312" t="inlineStr"/>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E312" t="inlineStr">
         <is>
           <t>-</t>
@@ -24006,7 +24014,7 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
@@ -25442,7 +25450,7 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
@@ -26286,7 +26294,11 @@
           <t>General and administration expenses 7a</t>
         </is>
       </c>
-      <c r="D353" t="inlineStr"/>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E353" t="inlineStr">
         <is>
           <t>-</t>
@@ -26768,7 +26780,7 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
@@ -27315,7 +27327,11 @@
           <t>General and administration expenses</t>
         </is>
       </c>
-      <c r="D370" t="inlineStr"/>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E370" t="inlineStr">
         <is>
           <t>-</t>
@@ -28669,7 +28685,7 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
@@ -28795,7 +28811,7 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E394" s="5" t="n">

--- a/output/pdf_financials_xlsx/TI.xlsx
+++ b/output/pdf_financials_xlsx/TI.xlsx
@@ -1396,22 +1396,22 @@
         <v>0</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0</v>
+        <v>0.158</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0</v>
+        <v>0.466</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0</v>
+        <v>0.415</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0</v>
+        <v>0.077</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0</v>
+        <v>0.067</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0</v>
+        <v>0.093</v>
       </c>
     </row>
     <row r="29">
@@ -1430,22 +1430,22 @@
         <v>-15.746</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-10.851</v>
+        <v>-10.693</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>1.284</v>
+        <v>1.75</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-24661.371</v>
+        <v>-24660.956</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-11.236</v>
+        <v>-11.159</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>4.499</v>
+        <v>4.566</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.486</v>
+        <v>-0.393</v>
       </c>
     </row>
     <row r="30">
@@ -1475,19 +1475,19 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>2.309601755585135</v>
+        <v>3.147821707378494</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-39737.30845458501</v>
+        <v>-39736.63975765779</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-21.57201551280574</v>
+        <v>-21.42418308182621</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>6.996780765462435</v>
+        <v>7.100978211847406</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-0.6546688937981572</v>
+        <v>-0.5293927474540655</v>
       </c>
     </row>
     <row r="31">
@@ -3842,22 +3842,22 @@
         <v>0</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>0.158</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>0.466</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>0.415</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>0.077</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>0.067</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>0.093</v>
       </c>
     </row>
     <row r="101">
@@ -11454,7 +11454,11 @@
           <t>Depreciation of right-of-use assets</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr"/>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E107" t="inlineStr">
         <is>
           <t>-</t>
@@ -13797,7 +13801,11 @@
           <t>Depreciation of right­of­use assets</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr"/>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E146" t="inlineStr">
         <is>
           <t>-</t>
@@ -15469,7 +15477,11 @@
           <t>Depreciation of right-of-use assets 11a</t>
         </is>
       </c>
-      <c r="D174" t="inlineStr"/>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E174" t="inlineStr">
         <is>
           <t>-</t>
@@ -17572,7 +17584,11 @@
           <t>Depreciation of right-of-use assets 11a, c</t>
         </is>
       </c>
-      <c r="D209" t="inlineStr"/>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E209" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/TI.xlsx
+++ b/output/pdf_financials_xlsx/TI.xlsx
@@ -1787,10 +1787,10 @@
         <v>0</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>0</v>
+        <v>0.012</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>0</v>
+        <v>0.096</v>
       </c>
       <c r="E40" s="3" t="n">
         <v>0</v>
@@ -1821,10 +1821,10 @@
         <v>0.001229</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>0.187</v>
+        <v>0.199</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>1.123</v>
+        <v>1.219</v>
       </c>
       <c r="E41" s="3" t="n">
         <v>0.655</v>
@@ -2847,10 +2847,10 @@
         <v>0</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>0</v>
+        <v>0.114</v>
       </c>
     </row>
     <row r="71">
@@ -2881,10 +2881,10 @@
         <v>0</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>0</v>
+        <v>0.114</v>
       </c>
     </row>
     <row r="72">
@@ -3017,10 +3017,10 @@
         <v>35.855</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>32.121</v>
+        <v>32.081</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>44.218</v>
+        <v>44.104</v>
       </c>
     </row>
     <row r="76">
@@ -3201,10 +3201,10 @@
         </is>
       </c>
       <c r="I80" s="3" t="n">
-        <v>0.02897102897102897</v>
+        <v>0.04229104229104229</v>
       </c>
       <c r="J80" s="3" t="n">
-        <v>0.02986257928118393</v>
+        <v>0.05998942917547569</v>
       </c>
     </row>
     <row r="81">
@@ -4176,13 +4176,13 @@
         <v>0</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.341</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
+        <v>0.391</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>0</v>
+        <v>0.275</v>
       </c>
       <c r="F110" s="3" t="n">
         <v>0</v>
@@ -4191,13 +4191,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="3" t="n">
-        <v>0</v>
+        <v>0.257</v>
       </c>
       <c r="I110" s="3" t="n">
-        <v>0</v>
+        <v>0.304</v>
       </c>
       <c r="J110" s="3" t="n">
-        <v>0</v>
+        <v>0.326</v>
       </c>
     </row>
     <row r="111">
@@ -4848,30 +4848,20 @@
       <c r="E129" s="3" t="n">
         <v>13.25</v>
       </c>
-      <c r="F129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F129" s="3" t="n">
+        <v>-4.132</v>
+      </c>
+      <c r="G129" s="3" t="n">
+        <v>-10.679</v>
+      </c>
+      <c r="H129" s="3" t="n">
+        <v>0.539</v>
+      </c>
+      <c r="I129" s="3" t="n">
+        <v>-7.383</v>
+      </c>
+      <c r="J129" s="3" t="n">
+        <v>7.42</v>
       </c>
     </row>
     <row r="130">
@@ -5062,30 +5052,20 @@
       <c r="E135" s="3" t="n">
         <v>-5.136</v>
       </c>
-      <c r="F135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F135" s="3" t="n">
+        <v>7.257</v>
+      </c>
+      <c r="G135" s="3" t="n">
+        <v>15.667</v>
+      </c>
+      <c r="H135" s="3" t="n">
+        <v>0.419</v>
+      </c>
+      <c r="I135" s="3" t="n">
+        <v>14.29</v>
+      </c>
+      <c r="J135" s="3" t="n">
+        <v>12.575</v>
       </c>
     </row>
   </sheetData>
@@ -5840,7 +5820,11 @@
           <t>Lease liabilities</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>-</t>
@@ -11218,7 +11202,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
           <t>-</t>
@@ -12306,7 +12294,11 @@
           <t>Net cash generated in operating activities</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr"/>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E121" t="inlineStr">
         <is>
           <t>-</t>
@@ -14474,7 +14466,11 @@
           <t>Net cash generated in operating activities</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr"/>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E157" t="inlineStr">
         <is>
           <t>-</t>
@@ -16431,7 +16427,11 @@
           <t>Net cash generated in operating activities</t>
         </is>
       </c>
-      <c r="D190" t="inlineStr"/>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E190" t="inlineStr">
         <is>
           <t>-</t>
@@ -17405,7 +17405,11 @@
           <t>Accretion expense 15</t>
         </is>
       </c>
-      <c r="D206" t="inlineStr"/>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E206" t="inlineStr">
         <is>
           <t>-</t>
@@ -19168,7 +19172,11 @@
           <t>Accretion 15</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr"/>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E235" t="inlineStr">
         <is>
           <t>-</t>
@@ -20203,7 +20211,11 @@
           <t>Accretion (Note 9)</t>
         </is>
       </c>
-      <c r="D252" t="inlineStr"/>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E252" t="inlineStr">
         <is>
           <t>-</t>
@@ -20894,7 +20906,11 @@
           <t>Proceeds on issuance of shares in private placement</t>
         </is>
       </c>
-      <c r="D263" t="inlineStr"/>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E263" s="5" t="n">
         <v>8.157679999999999</v>
       </c>
